--- a/artfynd/A 15470-2026 artfynd.xlsx
+++ b/artfynd/A 15470-2026 artfynd.xlsx
@@ -934,38 +934,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132888880</v>
+        <v>132888907</v>
       </c>
       <c r="B4" t="n">
-        <v>97995</v>
+        <v>79333</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>221945</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -973,10 +972,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>538372</v>
+        <v>538523</v>
       </c>
       <c r="R4" t="n">
-        <v>6999864</v>
+        <v>6999826</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1024,6 +1023,21 @@
       <c r="AH4" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
@@ -1041,41 +1055,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132888885</v>
+        <v>132888880</v>
       </c>
       <c r="B5" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1083,10 +1094,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538308</v>
+        <v>538372</v>
       </c>
       <c r="R5" t="n">
-        <v>6999835</v>
+        <v>6999864</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1121,11 +1132,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg med en knäckt stam.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1139,26 +1145,6 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1176,10 +1162,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132888907</v>
+        <v>132888885</v>
       </c>
       <c r="B6" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1187,26 +1173,30 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1214,10 +1204,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538523</v>
+        <v>538308</v>
       </c>
       <c r="R6" t="n">
-        <v>6999826</v>
+        <v>6999835</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1252,6 +1242,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg med en knäckt stam.</t>
+        </is>
+      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1269,17 +1264,22 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>gran</t>
+          <t>sälg</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>Picea abies</t>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132888879</v>
+        <v>132888910</v>
       </c>
       <c r="B15" t="n">
-        <v>97995</v>
+        <v>80473</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,27 +2331,30 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2359,10 +2362,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538536</v>
+        <v>538333</v>
       </c>
       <c r="R15" t="n">
-        <v>6999797</v>
+        <v>6999819</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2409,7 +2412,22 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2427,10 +2445,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132888910</v>
+        <v>132888879</v>
       </c>
       <c r="B16" t="n">
-        <v>80473</v>
+        <v>97995</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2438,30 +2456,27 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2469,10 +2484,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538333</v>
+        <v>538536</v>
       </c>
       <c r="R16" t="n">
-        <v>6999819</v>
+        <v>6999797</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2519,22 +2534,7 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132888852</v>
+        <v>132888865</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538477</v>
+        <v>538302</v>
       </c>
       <c r="R25" t="n">
-        <v>6999738</v>
+        <v>6999827</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132888865</v>
+        <v>132888852</v>
       </c>
       <c r="B26" t="n">
         <v>57958</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538302</v>
+        <v>538477</v>
       </c>
       <c r="R26" t="n">
-        <v>6999827</v>
+        <v>6999738</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">

--- a/artfynd/A 15470-2026 artfynd.xlsx
+++ b/artfynd/A 15470-2026 artfynd.xlsx
@@ -1055,38 +1055,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132888880</v>
+        <v>132888885</v>
       </c>
       <c r="B5" t="n">
-        <v>97995</v>
+        <v>80438</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221945</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1094,10 +1097,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>538372</v>
+        <v>538308</v>
       </c>
       <c r="R5" t="n">
-        <v>6999864</v>
+        <v>6999835</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1132,6 +1135,11 @@
           <t>2026-04-21</t>
         </is>
       </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>På en grov gammal sälg med en knäckt stam.</t>
+        </is>
+      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1145,6 +1153,26 @@
       <c r="AH5" t="inlineStr">
         <is>
           <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>Bark på levande träd</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1162,41 +1190,38 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132888885</v>
+        <v>132888880</v>
       </c>
       <c r="B6" t="n">
-        <v>80438</v>
+        <v>97995</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>221945</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1204,10 +1229,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>538308</v>
+        <v>538372</v>
       </c>
       <c r="R6" t="n">
-        <v>6999835</v>
+        <v>6999864</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1242,11 +1267,6 @@
           <t>2026-04-21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>På en grov gammal sälg med en knäckt stam.</t>
-        </is>
-      </c>
       <c r="AD6" t="b">
         <v>0</v>
       </c>
@@ -1260,26 +1280,6 @@
       <c r="AH6" t="inlineStr">
         <is>
           <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>Bark på levande träd</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>Bark on living woody plant # Salix caprea</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -2320,10 +2320,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132888910</v>
+        <v>132888879</v>
       </c>
       <c r="B15" t="n">
-        <v>80473</v>
+        <v>97995</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2331,30 +2331,27 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>221945</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>med soral</t>
-        </is>
-      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2362,10 +2359,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>538333</v>
+        <v>538536</v>
       </c>
       <c r="R15" t="n">
-        <v>6999819</v>
+        <v>6999797</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2412,22 +2409,7 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>Barrskog</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
+          <t>Granskog</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2445,10 +2427,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132888879</v>
+        <v>132888910</v>
       </c>
       <c r="B16" t="n">
-        <v>97995</v>
+        <v>80473</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2456,27 +2438,30 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221945</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr"/>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>med soral</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2484,10 +2469,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>538536</v>
+        <v>538333</v>
       </c>
       <c r="R16" t="n">
-        <v>6999797</v>
+        <v>6999819</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2534,7 +2519,22 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>Granskog</t>
+          <t>Barrskog</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -3570,7 +3570,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132888865</v>
+        <v>132888852</v>
       </c>
       <c r="B25" t="n">
         <v>57958</v>
@@ -3613,10 +3613,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>538302</v>
+        <v>538477</v>
       </c>
       <c r="R25" t="n">
-        <v>6999827</v>
+        <v>6999738</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3653,7 +3653,7 @@
       </c>
       <c r="AC25" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
+          <t>Ringhack (savhack), färska, på en gran.</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3705,7 +3705,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132888852</v>
+        <v>132888865</v>
       </c>
       <c r="B26" t="n">
         <v>57958</v>
@@ -3748,10 +3748,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>538477</v>
+        <v>538302</v>
       </c>
       <c r="R26" t="n">
-        <v>6999738</v>
+        <v>6999827</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3788,7 +3788,7 @@
       </c>
       <c r="AC26" t="inlineStr">
         <is>
-          <t>Ringhack (savhack), färska, på en gran.</t>
+          <t>Ringhack (savhack), färska, längs flera meter på en gran.</t>
         </is>
       </c>
       <c r="AD26" t="b">
